--- a/src/test/resources/TestData - NinzaCRM.xlsx
+++ b/src/test/resources/TestData - NinzaCRM.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="11_88C076A97ED3D73C50525412CE576B26A35F0A95" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA38AEE7-85CE-4512-8450-76991EC745EA}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" activeTab="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Integration" sheetId="1" r:id="rId1"/>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="150">
   <si>
     <t>TC_ID</t>
   </si>
@@ -443,12 +444,39 @@
   </si>
   <si>
     <t>VivoBook Invoice_5</t>
+  </si>
+  <si>
+    <t>Target Size</t>
+  </si>
+  <si>
+    <t>Rating</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>9886697556</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>9886695774</t>
+  </si>
+  <si>
+    <t>Ratings</t>
+  </si>
+  <si>
+    <t>Probability</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -505,7 +533,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -522,10 +550,13 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -543,6 +574,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -807,17 +842,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y30"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AB30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29.54296875" style="4" customWidth="1"/>
     <col min="2" max="2" width="37.6328125" style="4" customWidth="1"/>
-    <col min="3" max="25" width="25.6328125" style="4" customWidth="1"/>
-    <col min="26" max="16384" width="8.7265625" style="4"/>
+    <col min="3" max="28" width="25.6328125" style="4" customWidth="1"/>
+    <col min="29" max="16384" width="8.7265625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -827,26 +862,32 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
+      <c r="L1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>143</v>
+      </c>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -859,8 +900,11 @@
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
@@ -870,27 +914,33 @@
       <c r="C2" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
+      <c r="L2" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="N2" s="8"/>
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
       <c r="Q2" s="3"/>
@@ -902,12 +952,15 @@
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
+      <c r="AB2" s="3"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
+      <c r="D3" s="8"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
@@ -929,8 +982,11 @@
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
-    </row>
-    <row r="4" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
+    </row>
+    <row r="4" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -941,18 +997,20 @@
         <v>2</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -970,8 +1028,11 @@
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z4" s="1"/>
+      <c r="AA4" s="1"/>
+      <c r="AB4" s="1"/>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
@@ -981,19 +1042,21 @@
       <c r="C5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="3">
-        <v>9876567897</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
@@ -1011,12 +1074,14 @@
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
+      <c r="AB5" s="3"/>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -1038,8 +1103,11 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
-    </row>
-    <row r="7" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
+      <c r="AB6" s="3"/>
+    </row>
+    <row r="7" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -1050,39 +1118,47 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="M7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="N7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="O7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="P7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
+      <c r="Q7" s="1" t="s">
+        <v>149</v>
+      </c>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
@@ -1091,8 +1167,11 @@
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z7" s="1"/>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="1"/>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>12</v>
       </c>
@@ -1102,40 +1181,48 @@
       <c r="C8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="J8" s="3">
-        <v>5000</v>
-      </c>
-      <c r="K8" s="3" t="s">
+      <c r="M8" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="N8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="O8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="P8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
+      <c r="Q8" s="8" t="s">
+        <v>145</v>
+      </c>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
@@ -1144,8 +1231,11 @@
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
+      <c r="AB8" s="3"/>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -1171,8 +1261,11 @@
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
-    </row>
-    <row r="10" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="Z9" s="3"/>
+      <c r="AA9" s="3"/>
+      <c r="AB9" s="3"/>
+    </row>
+    <row r="10" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1182,74 +1275,77 @@
       <c r="C10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="1"/>
+      <c r="E10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="M10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="N10" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="O10" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="P10" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="N10" s="1" t="s">
+      <c r="Q10" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="O10" s="1" t="s">
+      <c r="R10" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="P10" s="1" t="s">
+      <c r="S10" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="Q10" s="1" t="s">
+      <c r="T10" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="R10" s="1" t="s">
+      <c r="U10" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="S10" s="1" t="s">
+      <c r="V10" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="T10" s="1" t="s">
+      <c r="W10" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="U10" s="1" t="s">
+      <c r="X10" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="V10" s="1" t="s">
+      <c r="Y10" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="W10" s="1" t="s">
+      <c r="Z10" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="X10" s="1" t="s">
+      <c r="AA10" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="Y10" s="1" t="s">
+      <c r="AB10" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>13</v>
       </c>
@@ -1259,74 +1355,77 @@
       <c r="C11" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="3"/>
+      <c r="E11" s="3">
         <v>5000</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="I11" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="M11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="N11" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="L11" s="3" t="s">
+      <c r="O11" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="M11" s="5">
+      <c r="P11" s="5">
         <v>45856</v>
       </c>
-      <c r="N11" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="O11" s="3" t="s">
+      <c r="Q11" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="R11" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="P11" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q11" s="3" t="s">
+      <c r="S11" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="T11" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="R11" s="3">
+      <c r="U11" s="3">
         <v>731204</v>
       </c>
-      <c r="S11" s="3" t="s">
+      <c r="V11" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="T11" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="U11" s="3" t="s">
+      <c r="W11" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="X11" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="V11" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="W11" s="3" t="s">
+      <c r="Y11" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z11" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="X11" s="3">
+      <c r="AA11" s="3">
         <v>731204</v>
       </c>
-      <c r="Y11" s="3" t="s">
+      <c r="AB11" s="3" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -1352,8 +1451,11 @@
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
-    </row>
-    <row r="13" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="Z12" s="3"/>
+      <c r="AA12" s="3"/>
+      <c r="AB12" s="3"/>
+    </row>
+    <row r="13" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
@@ -1363,68 +1465,71 @@
       <c r="C13" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="1"/>
+      <c r="E13" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="M13" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="N13" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="O13" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="P13" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="N13" s="1" t="s">
+      <c r="Q13" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="O13" s="1" t="s">
+      <c r="R13" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="P13" s="1" t="s">
+      <c r="S13" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="Q13" s="1" t="s">
+      <c r="T13" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="R13" s="1" t="s">
+      <c r="U13" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="S13" s="1" t="s">
+      <c r="V13" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="T13" s="1" t="s">
+      <c r="W13" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="U13" s="1" t="s">
+      <c r="X13" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="V13" s="1" t="s">
+      <c r="Y13" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="W13" s="1"/>
-      <c r="X13" s="1"/>
-      <c r="Y13" s="1"/>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z13" s="1"/>
+      <c r="AA13" s="1"/>
+      <c r="AB13" s="1"/>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>14</v>
       </c>
@@ -1434,68 +1539,71 @@
       <c r="C14" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="3"/>
+      <c r="E14" s="5">
         <v>45856</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="J14" s="5">
+      <c r="M14" s="5">
         <v>45856</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="L14" s="3" t="s">
+      <c r="N14" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="O14" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="N14" s="3" t="s">
+      <c r="P14" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q14" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="O14" s="3">
+      <c r="R14" s="3">
         <v>731204</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="R14" s="3" t="s">
+      <c r="T14" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="U14" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="T14" s="3" t="s">
+      <c r="V14" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="W14" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="U14" s="3">
+      <c r="X14" s="3">
         <v>731204</v>
       </c>
-      <c r="V14" s="3" t="s">
+      <c r="Y14" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z14" s="3"/>
+      <c r="AA14" s="3"/>
+      <c r="AB14" s="3"/>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -1504,9 +1612,9 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
@@ -1521,8 +1629,11 @@
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
-    </row>
-    <row r="16" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="Z15" s="3"/>
+      <c r="AA15" s="3"/>
+      <c r="AB15" s="3"/>
+    </row>
+    <row r="16" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
@@ -1532,72 +1643,75 @@
       <c r="C16" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="1"/>
+      <c r="E16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="I16" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="M16" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="N16" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="L16" s="1" t="s">
+      <c r="O16" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="P16" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="N16" s="1" t="s">
+      <c r="Q16" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="O16" s="1" t="s">
+      <c r="R16" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="P16" s="1" t="s">
+      <c r="S16" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="Q16" s="1" t="s">
+      <c r="T16" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="R16" s="1" t="s">
+      <c r="U16" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="S16" s="1" t="s">
+      <c r="V16" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="T16" s="1" t="s">
+      <c r="W16" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="U16" s="1" t="s">
+      <c r="X16" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="V16" s="1" t="s">
+      <c r="Y16" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="W16" s="1" t="s">
+      <c r="Z16" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="X16" s="1" t="s">
+      <c r="AA16" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="Y16" s="1"/>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="AB16" s="1"/>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
@@ -1607,72 +1721,75 @@
       <c r="C17" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="3"/>
+      <c r="E17" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9876567889</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H17" s="3" t="s">
+      <c r="I17" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="J17" s="3" t="s">
+      <c r="M17" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="K17" s="3" t="s">
+      <c r="N17" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="L17" s="5">
+      <c r="O17" s="5">
         <v>45856</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="N17" s="3" t="s">
+      <c r="P17" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q17" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="P17" s="3" t="s">
+      <c r="R17" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="S17" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="T17" s="3">
         <v>731204</v>
       </c>
-      <c r="R17" s="3" t="s">
+      <c r="U17" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="T17" s="3" t="s">
+      <c r="V17" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="W17" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="V17" s="3" t="s">
+      <c r="X17" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y17" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Z17" s="3">
         <v>731204</v>
       </c>
-      <c r="X17" s="3" t="s">
+      <c r="AA17" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="Y17" s="3"/>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="AB17" s="3"/>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -1698,8 +1815,11 @@
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
-    </row>
-    <row r="19" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="Z18" s="3"/>
+      <c r="AA18" s="3"/>
+      <c r="AB18" s="3"/>
+    </row>
+    <row r="19" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>0</v>
       </c>
@@ -1709,72 +1829,75 @@
       <c r="C19" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="1"/>
+      <c r="E19" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="F19" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="G19" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="H19" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="I19" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="M19" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="N19" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="L19" s="1" t="s">
+      <c r="O19" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="M19" s="1" t="s">
+      <c r="P19" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="N19" s="1" t="s">
+      <c r="Q19" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="O19" s="1" t="s">
+      <c r="R19" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="P19" s="1" t="s">
+      <c r="S19" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="Q19" s="1" t="s">
+      <c r="T19" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="R19" s="1" t="s">
+      <c r="U19" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="S19" s="1" t="s">
+      <c r="V19" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="T19" s="1" t="s">
+      <c r="W19" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="U19" s="1" t="s">
+      <c r="X19" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="V19" s="1" t="s">
+      <c r="Y19" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="W19" s="1" t="s">
+      <c r="Z19" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="X19" s="1" t="s">
+      <c r="AA19" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="Y19" s="1"/>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="AB19" s="1"/>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>16</v>
       </c>
@@ -1784,72 +1907,75 @@
       <c r="C20" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="3"/>
+      <c r="E20" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>10</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>80000</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="I20" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="M20" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="N20" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="L20" s="5">
+      <c r="O20" s="5">
         <v>45856</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="N20" s="3" t="s">
+      <c r="P20" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q20" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="P20" s="3" t="s">
+      <c r="R20" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="S20" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="T20" s="3">
         <v>731204</v>
       </c>
-      <c r="R20" s="3" t="s">
+      <c r="U20" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="T20" s="3" t="s">
+      <c r="V20" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="W20" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="V20" s="3" t="s">
+      <c r="X20" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y20" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Z20" s="3">
         <v>731204</v>
       </c>
-      <c r="X20" s="3" t="s">
+      <c r="AA20" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="Y20" s="3"/>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="AB20" s="3"/>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1875,8 +2001,11 @@
       <c r="W21" s="3"/>
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
-    </row>
-    <row r="22" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="Z21" s="3"/>
+      <c r="AA21" s="3"/>
+      <c r="AB21" s="3"/>
+    </row>
+    <row r="22" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>0</v>
       </c>
@@ -1886,70 +2015,73 @@
       <c r="C22" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="1"/>
+      <c r="E22" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="F22" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="G22" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="M22" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="N22" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="L22" s="1" t="s">
+      <c r="O22" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="M22" s="1" t="s">
+      <c r="P22" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="N22" s="1" t="s">
+      <c r="Q22" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O22" s="1" t="s">
+      <c r="R22" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="P22" s="1" t="s">
+      <c r="S22" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="Q22" s="1" t="s">
+      <c r="T22" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="R22" s="1" t="s">
+      <c r="U22" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="S22" s="1" t="s">
+      <c r="V22" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="T22" s="1" t="s">
+      <c r="W22" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="U22" s="1" t="s">
+      <c r="X22" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="V22" s="1" t="s">
+      <c r="Y22" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="W22" s="1" t="s">
+      <c r="Z22" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="X22" s="1"/>
-      <c r="Y22" s="1"/>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="AA22" s="1"/>
+      <c r="AB22" s="1"/>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>17</v>
       </c>
@@ -1959,70 +2091,73 @@
       <c r="C23" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="D23" s="3"/>
+      <c r="E23" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>10</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>90000</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="I23" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="M23" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="K23" s="5">
+      <c r="N23" s="5">
         <v>45856</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="M23" s="3" t="s">
+      <c r="O23" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="P23" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="O23" s="3" t="s">
+      <c r="Q23" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="R23" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="P23" s="3">
+      <c r="S23" s="3">
         <v>731204</v>
       </c>
-      <c r="Q23" s="3" t="s">
+      <c r="T23" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="S23" s="3" t="s">
+      <c r="U23" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="V23" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="U23" s="3" t="s">
+      <c r="W23" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="X23" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="V23" s="3">
+      <c r="Y23" s="3">
         <v>731204</v>
       </c>
-      <c r="W23" s="3" t="s">
+      <c r="Z23" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="X23" s="3"/>
-      <c r="Y23" s="3"/>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="AA23" s="3"/>
+      <c r="AB23" s="3"/>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -2048,8 +2183,11 @@
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
-    </row>
-    <row r="25" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="Z24" s="3"/>
+      <c r="AA24" s="3"/>
+      <c r="AB24" s="3"/>
+    </row>
+    <row r="25" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
@@ -2059,70 +2197,73 @@
       <c r="C25" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="1"/>
+      <c r="E25" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="G25" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="H25" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="I25" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="M25" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="N25" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="L25" s="1" t="s">
+      <c r="O25" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="M25" s="1" t="s">
+      <c r="P25" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="N25" s="1" t="s">
+      <c r="Q25" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="O25" s="1" t="s">
+      <c r="R25" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="P25" s="1" t="s">
+      <c r="S25" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="Q25" s="1" t="s">
+      <c r="T25" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="R25" s="1" t="s">
+      <c r="U25" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="S25" s="1" t="s">
+      <c r="V25" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="T25" s="1" t="s">
+      <c r="W25" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="U25" s="1" t="s">
+      <c r="X25" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="V25" s="1" t="s">
+      <c r="Y25" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="W25" s="1" t="s">
+      <c r="Z25" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="X25" s="1"/>
-      <c r="Y25" s="1"/>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="AA25" s="1"/>
+      <c r="AB25" s="1"/>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>18</v>
       </c>
@@ -2132,70 +2273,73 @@
       <c r="C26" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="3"/>
+      <c r="E26" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>9876567809</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="G26" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="H26" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="I26" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="I26" s="6" t="s">
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="J26" s="3" t="s">
+      <c r="M26" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="K26" s="5">
+      <c r="N26" s="5">
         <v>45856</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="M26" s="3" t="s">
+      <c r="O26" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="P26" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="O26" s="3" t="s">
+      <c r="Q26" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="R26" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="P26" s="3">
+      <c r="S26" s="3">
         <v>731204</v>
       </c>
-      <c r="Q26" s="3" t="s">
+      <c r="T26" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="S26" s="3" t="s">
+      <c r="U26" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="V26" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="U26" s="3" t="s">
+      <c r="W26" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="X26" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="V26" s="3">
+      <c r="Y26" s="3">
         <v>731204</v>
       </c>
-      <c r="W26" s="3" t="s">
+      <c r="Z26" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="X26" s="3"/>
-      <c r="Y26" s="3"/>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="AA26" s="3"/>
+      <c r="AB26" s="3"/>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -2221,8 +2365,11 @@
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
-    </row>
-    <row r="28" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="Z27" s="3"/>
+      <c r="AA27" s="3"/>
+      <c r="AB27" s="3"/>
+    </row>
+    <row r="28" spans="1:28" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>0</v>
       </c>
@@ -2232,66 +2379,69 @@
       <c r="C28" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="1"/>
+      <c r="E28" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="F28" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="G28" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="H28" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="I28" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="M28" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="N28" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="L28" s="1" t="s">
+      <c r="O28" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="M28" s="1" t="s">
+      <c r="P28" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="N28" s="1" t="s">
+      <c r="Q28" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="O28" s="1" t="s">
+      <c r="R28" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="P28" s="1" t="s">
+      <c r="S28" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="Q28" s="1" t="s">
+      <c r="T28" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="R28" s="1" t="s">
+      <c r="U28" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="S28" s="1" t="s">
+      <c r="V28" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="T28" s="1" t="s">
+      <c r="W28" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="U28" s="1" t="s">
+      <c r="X28" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="V28" s="1"/>
-      <c r="W28" s="1"/>
-      <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z28" s="1"/>
+      <c r="AA28" s="1"/>
+      <c r="AB28" s="1"/>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>19</v>
       </c>
@@ -2301,66 +2451,69 @@
       <c r="C29" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="D29" s="3"/>
+      <c r="E29" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="F29" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="G29" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="H29" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="H29" s="3" t="s">
+      <c r="I29" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="I29" s="5">
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="5">
         <v>45856</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="K29" s="3" t="s">
+      <c r="M29" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="N29" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="M29" s="3" t="s">
+      <c r="O29" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="P29" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="N29" s="3">
+      <c r="Q29" s="3">
         <v>731204</v>
       </c>
-      <c r="O29" s="3" t="s">
+      <c r="R29" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q29" s="3" t="s">
+      <c r="S29" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="T29" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="S29" s="3" t="s">
+      <c r="U29" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="V29" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="T29" s="3">
+      <c r="W29" s="3">
         <v>731204</v>
       </c>
-      <c r="U29" s="3" t="s">
+      <c r="X29" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="V29" s="3"/>
-      <c r="W29" s="3"/>
-      <c r="X29" s="3"/>
       <c r="Y29" s="3"/>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="Z29" s="3"/>
+      <c r="AA29" s="3"/>
+      <c r="AB29" s="3"/>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -2386,14 +2539,18 @@
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
       <c r="Y30" s="3"/>
+      <c r="Z30" s="3"/>
+      <c r="AA30" s="3"/>
+      <c r="AB30" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AH29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2667,10 +2824,10 @@
       <c r="AH4" s="1"/>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>53</v>
       </c>
       <c r="C5" s="3" t="s">
